--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/14_metrics_outcomes.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/14_metrics_outcomes.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R0cea5df619ce47e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rd0be90a595ac4cba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rc6c4753623f54de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R750285be20b14dd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rd5f67849a07d4020"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rb6aec528013c4394"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R6b34f570ed1c4fb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R13ca023f31ee4c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R931202aa6d85420a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R77cc8d6703c64b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R7ca6414496604b3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R8ff3fdfea47442ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2059c88498e4f45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab3984a40efd4843"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -809,7 +809,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Executive Office cycle time (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -859,7 +859,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm Executive Office quality and exception rate (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -909,7 +909,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Attach client evidence for Retail Deposits and Branch Operations cycle time (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>Medium</x:v>
@@ -959,7 +959,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Reconcile Retail Deposits and Branch Operations quality and exception rate (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>Medium</x:v>
@@ -1009,7 +1009,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Commercial Lending and Treasury cycle time (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>Medium</x:v>
@@ -1059,7 +1059,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Commercial Lending and Treasury quality and exception rate (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>Medium</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm Cards Operations cycle time (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>Medium</x:v>
@@ -1159,7 +1159,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Attach client evidence for Cards Operations quality and exception rate (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>Medium</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Reconcile Payments Operations cycle time (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>Medium</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations quality and exception rate (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>Medium</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Consumer Lending Operations cycle time (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>Medium</x:v>
@@ -1359,7 +1359,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm Consumer Lending Operations quality and exception rate (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>Medium</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Attach client evidence for Wealth Advisory and Brokerage cycle time (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>Medium</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Reconcile Wealth Advisory and Brokerage quality and exception rate (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>Medium</x:v>
@@ -1482,7 +1482,7 @@
         <x:v>Fraud / risk modernization and readiness program</x:v>
       </x:c>
       <x:c r="F20" t="str">
-        <x:v>Elapsed time or throughput measure for fraud alerts, case triage, AML/transaction monitoring, loss prevention.</x:v>
+        <x:v>Confirmed fraud loss avoided / recovered amount baseline for Fraud Analyst Copilot; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G20" t="str">
         <x:v>9 days / 2050 monthly events synthetic</x:v>
@@ -1497,7 +1497,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>Fraud Risk Operations Operational Dataset</x:v>
+        <x:v>Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="L20" t="str">
         <x:v>Synthetic baseline for template depth proof; not realized value.</x:v>
@@ -1506,10 +1506,10 @@
         <x:v>CRO</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Candidate baseline only</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Fraud and Risk Operations cycle time (record 15) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>Medium</x:v>
@@ -1532,7 +1532,7 @@
         <x:v>Fraud / risk modernization and readiness program</x:v>
       </x:c>
       <x:c r="F21" t="str">
-        <x:v>Exception, defect, rework, denial, or issue rate for Fraud and Risk Operations.</x:v>
+        <x:v>Fraud alert precision by model version for Fraud Analyst Copilot; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G21" t="str">
         <x:v>3% synthetic exception rate</x:v>
@@ -1547,7 +1547,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>Fraud Risk Operations Analytics Mart</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.</x:v>
       </x:c>
       <x:c r="L21" t="str">
         <x:v>Planning-grade synthetic metric; requires source evidence.</x:v>
@@ -1556,10 +1556,10 @@
         <x:v>CRO</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Needs validation</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Fraud and Risk Operations quality and exception rate (record 16) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>Medium</x:v>
@@ -1609,7 +1609,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm Compliance and Model Risk Management cycle time (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>Medium</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Attach client evidence for Compliance and Model Risk Management quality and exception rate (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>Medium</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Reconcile Contact Center and Servicing cycle time (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>Medium</x:v>
@@ -1759,7 +1759,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing quality and exception rate (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>Medium</x:v>
@@ -1809,7 +1809,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Digital Account Opening and Onboarding cycle time (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P26" t="str">
         <x:v>Medium</x:v>
@@ -1859,7 +1859,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm Digital Account Opening and Onboarding quality and exception rate (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P27" t="str">
         <x:v>Medium</x:v>
@@ -1909,7 +1909,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Attach client evidence for Core Banking Modernization cycle time (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P28" t="str">
         <x:v>Medium</x:v>
@@ -1959,7 +1959,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Reconcile Core Banking Modernization quality and exception rate (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P29" t="str">
         <x:v>Medium</x:v>
@@ -2009,7 +2009,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Customer 360 Data Product cycle time (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P30" t="str">
         <x:v>Medium</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Customer 360 Data Product quality and exception rate (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P31" t="str">
         <x:v>Medium</x:v>
@@ -2109,7 +2109,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm Retail Banking Analytics cycle time (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P32" t="str">
         <x:v>Medium</x:v>
@@ -2159,7 +2159,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Attach client evidence for Retail Banking Analytics quality and exception rate (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P33" t="str">
         <x:v>Medium</x:v>
@@ -2209,7 +2209,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Reconcile Cards Portfolio Analytics cycle time (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P34" t="str">
         <x:v>Medium</x:v>
@@ -2259,7 +2259,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics quality and exception rate (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P35" t="str">
         <x:v>Medium</x:v>
@@ -2309,7 +2309,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Payments and Settlement Analytics cycle time (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P36" t="str">
         <x:v>Medium</x:v>
@@ -2359,7 +2359,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm Payments and Settlement Analytics quality and exception rate (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P37" t="str">
         <x:v>Medium</x:v>
@@ -2382,7 +2382,7 @@
         <x:v>Fraud/risk analytics modernization and readiness program</x:v>
       </x:c>
       <x:c r="F38" t="str">
-        <x:v>Elapsed time or throughput measure for fraud scores, alert productivity, loss trends, risk segmentation.</x:v>
+        <x:v>Confirmed fraud loss avoided / recovered amount baseline for Fraud Analyst Copilot; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G38" t="str">
         <x:v>2 days / 3400 monthly events synthetic</x:v>
@@ -2397,7 +2397,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>Fraud Risk Analytics Operational Dataset</x:v>
+        <x:v>AML transaction monitoring source inventory and control-owner interview.</x:v>
       </x:c>
       <x:c r="L38" t="str">
         <x:v>Synthetic baseline for template depth proof; not realized value.</x:v>
@@ -2406,10 +2406,10 @@
         <x:v>Fraud Analytics Lead</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>Candidate baseline only</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Fraud and Risk Analytics cycle time (record 33) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P38" t="str">
         <x:v>Medium</x:v>
@@ -2432,7 +2432,7 @@
         <x:v>Fraud/risk analytics modernization and readiness program</x:v>
       </x:c>
       <x:c r="F39" t="str">
-        <x:v>Exception, defect, rework, denial, or issue rate for Fraud and Risk Analytics.</x:v>
+        <x:v>Fraud alert precision by model version for Fraud Analyst Copilot; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G39" t="str">
         <x:v>5% synthetic exception rate</x:v>
@@ -2447,7 +2447,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>Fraud Risk Analytics Analytics Mart</x:v>
+        <x:v>Digital onboarding/KYC vendor report with identity verification and device-risk signals.</x:v>
       </x:c>
       <x:c r="L39" t="str">
         <x:v>Planning-grade synthetic metric; requires source evidence.</x:v>
@@ -2456,10 +2456,10 @@
         <x:v>Fraud Analytics Lead</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Needs validation</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Fraud and Risk Analytics quality and exception rate (record 34) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P39" t="str">
         <x:v>Medium</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cloud Data Platform cycle time (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P40" t="str">
         <x:v>Medium</x:v>
@@ -2559,7 +2559,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Cloud Data Platform quality and exception rate (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P41" t="str">
         <x:v>Medium</x:v>
@@ -2609,7 +2609,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O42" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline cycle time (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P42" t="str">
         <x:v>Medium</x:v>
@@ -2659,7 +2659,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O43" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline quality and exception rate (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P43" t="str">
         <x:v>Medium</x:v>
@@ -2709,7 +2709,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization cycle time (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P44" t="str">
         <x:v>Medium</x:v>
@@ -2759,7 +2759,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization quality and exception rate (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P45" t="str">
         <x:v>Medium</x:v>
@@ -2809,7 +2809,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O46" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Infrastructure and CMDB cycle time (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P46" t="str">
         <x:v>Medium</x:v>
@@ -2859,7 +2859,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O47" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm Infrastructure and CMDB quality and exception rate (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P47" t="str">
         <x:v>Medium</x:v>
@@ -2909,7 +2909,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O48" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Attach client evidence for Incident Problem Change Operations cycle time (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P48" t="str">
         <x:v>Medium</x:v>
@@ -2959,7 +2959,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O49" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations quality and exception rate (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P49" t="str">
         <x:v>Medium</x:v>
@@ -2983,7 +2983,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65a12105095e4611"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcbaa83070a34137"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3058,7 +3058,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree3ad9efdbaf4a8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42489ee2cbdf43c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3252,7 +3252,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c4d5e13484c4312"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87056cc4d0b24ea6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3322,7 +3322,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d22adb93bc342cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bf65de61f1a484b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3432,7 +3432,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37a53e67bce6415a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9be4a00ddd54781"/>
   </x:tableParts>
 </x:worksheet>
 </file>